--- a/CAT-2.xlsx
+++ b/CAT-2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vrish\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vrish\Downloads\STS MCQS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5063A295-5937-4CE1-BCB6-5A11AC9EB487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D78AA56-527B-4123-A43A-A0F405945ACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D974F089-E0CA-4CEB-975A-A17D36675E11}"/>
   </bookViews>
@@ -6611,11 +6611,13 @@
       <c r="C105" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="D105" s="2" t="e">
-        <v>#NAME?</v>
-      </c>
-      <c r="E105" s="2" t="e">
-        <v>#NAME?</v>
+      <c r="D105" s="2" t="str">
+        <f>"-h to h"</f>
+        <v>-h to h</v>
+      </c>
+      <c r="E105" s="2" t="str">
+        <f>"-h to 0"</f>
+        <v>-h to 0</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>399</v>
